--- a/artfynd/A 48356-2019 artfynd.xlsx
+++ b/artfynd/A 48356-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48356-2019 artfynd.xlsx
+++ b/artfynd/A 48356-2019 artfynd.xlsx
@@ -1676,10 +1676,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117689907</v>
+        <v>117689928</v>
       </c>
       <c r="B10" t="n">
-        <v>56751</v>
+        <v>57510</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1688,37 +1688,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102961</v>
+        <v>102981</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117689928</v>
+        <v>117689940</v>
       </c>
       <c r="B12" t="n">
-        <v>57510</v>
+        <v>57382</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1936,37 +1936,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102981</v>
+        <v>102626</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117689940</v>
+        <v>117689907</v>
       </c>
       <c r="B13" t="n">
-        <v>57382</v>
+        <v>56751</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2060,20 +2060,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102626</v>
+        <v>102961</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2090,7 +2090,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>

--- a/artfynd/A 48356-2019 artfynd.xlsx
+++ b/artfynd/A 48356-2019 artfynd.xlsx
@@ -1676,10 +1676,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117689928</v>
+        <v>117689907</v>
       </c>
       <c r="B10" t="n">
-        <v>57510</v>
+        <v>56752</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1688,37 +1688,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102981</v>
+        <v>102961</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117689861</v>
+        <v>117689928</v>
       </c>
       <c r="B11" t="n">
-        <v>57789</v>
+        <v>57511</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1812,20 +1812,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102995</v>
+        <v>102981</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1835,14 +1835,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1927,7 +1927,7 @@
         <v>117689940</v>
       </c>
       <c r="B12" t="n">
-        <v>57382</v>
+        <v>57383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117689907</v>
+        <v>117689861</v>
       </c>
       <c r="B13" t="n">
-        <v>56751</v>
+        <v>57790</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2064,26 +2064,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102961</v>
+        <v>102995</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>

--- a/artfynd/A 48356-2019 artfynd.xlsx
+++ b/artfynd/A 48356-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1800,49 +1800,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117689861</v>
+        <v>117689940</v>
       </c>
       <c r="B11" t="n">
-        <v>57790</v>
+        <v>57403</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102995</v>
+        <v>102626</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1921,254 +1921,6 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>117689940</v>
-      </c>
-      <c r="B12" t="n">
-        <v>57403</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>102626</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Törnskata</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Lanius collurio</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Porsen, Älje-Porsens naturreservat, Uddevalla, Boh</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>325921</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6472128</v>
-      </c>
-      <c r="S12" t="n">
-        <v>25</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Uddevalla</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Uddevalla</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Lars-Erik Hammar</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Lars-Erik Hammar</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>117689907</v>
-      </c>
-      <c r="B13" t="n">
-        <v>56752</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>102961</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Drillsnäppa</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Actitis hypoleucos</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Porsen, Älje-Porsens naturreservat, Uddevalla, Boh</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>325921</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6472128</v>
-      </c>
-      <c r="S13" t="n">
-        <v>25</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Uddevalla</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Uddevalla</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Lars-Erik Hammar</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Lars-Erik Hammar</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
